--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Bharat Consumption Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Bharat Consumption Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="189">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Bharat Consumption Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,24 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
     <t>Bharti Airtel Ltd.</t>
   </si>
   <si>
@@ -70,13 +88,10 @@
     <t>Telecom - Services</t>
   </si>
   <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
   </si>
   <si>
     <t>Maruti Suzuki India Ltd.</t>
@@ -85,13 +100,13 @@
     <t>INE585B01010</t>
   </si>
   <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
   </si>
   <si>
     <t>Nestle India Ltd.</t>
@@ -103,19 +118,13 @@
     <t>Food Products</t>
   </si>
   <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Retailing</t>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
     <t>TVS Motor Company Ltd.</t>
@@ -130,6 +139,27 @@
     <t>INE216A01030</t>
   </si>
   <si>
+    <t>Trent Ltd.</t>
+  </si>
+  <si>
+    <t>INE849A01020</t>
+  </si>
+  <si>
+    <t>United Breweries Ltd.</t>
+  </si>
+  <si>
+    <t>INE686F01025</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Vedant Fashions Ltd.</t>
+  </si>
+  <si>
+    <t>INE825V01034</t>
+  </si>
+  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -139,22 +169,19 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>Pidilite Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>United Breweries Ltd.</t>
-  </si>
-  <si>
-    <t>INE686F01025</t>
-  </si>
-  <si>
-    <t>Beverages</t>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
   </si>
   <si>
     <t>Havells India Ltd.</t>
@@ -166,52 +193,103 @@
     <t>Consumer Durables</t>
   </si>
   <si>
+    <t>International Gemmological Institute (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE0Q9301021</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>RR Kabel Ltd.</t>
+  </si>
+  <si>
+    <t>INE777K01022</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Eureka Forbes Ltd.</t>
+  </si>
+  <si>
+    <t>INE0KCE01017</t>
+  </si>
+  <si>
+    <t>Honasa Consumer Ltd.</t>
+  </si>
+  <si>
+    <t>INE0J5401028</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Crompton Greaves Consumer Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE299U01018</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
     <t>Hero Motocorp Ltd.</t>
   </si>
   <si>
     <t>INE158A01026</t>
   </si>
   <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>International Gemmological Institute (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q9301021</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Trent Ltd.</t>
-  </si>
-  <si>
-    <t>INE849A01020</t>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
   </si>
   <si>
     <t>Godrej Consumer Products Ltd.</t>
@@ -220,28 +298,10 @@
     <t>INE102D01028</t>
   </si>
   <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>Vedant Fashions Ltd.</t>
-  </si>
-  <si>
-    <t>INE825V01034</t>
-  </si>
-  <si>
-    <t>RR Kabel Ltd.</t>
-  </si>
-  <si>
-    <t>INE777K01022</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
   </si>
   <si>
     <t>Red Tape Ltd</t>
@@ -250,13 +310,34 @@
     <t>INE0LXT01019</t>
   </si>
   <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>La Opala RG Ltd.</t>
+  </si>
+  <si>
+    <t>INE059D01020</t>
+  </si>
+  <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Sanofi Consumer Healthcare India Ltd</t>
+  </si>
+  <si>
+    <t>INE0UOS01011</t>
+  </si>
+  <si>
+    <t>Whirlpool of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE716A01013</t>
   </si>
   <si>
     <t>Asian Paints Ltd.</t>
@@ -265,31 +346,112 @@
     <t>INE021A01026</t>
   </si>
   <si>
+    <t>Procter &amp; Gamble Health Ltd.</t>
+  </si>
+  <si>
+    <t>INE199A01012</t>
+  </si>
+  <si>
+    <t>Kajaria Ceramics Ltd.</t>
+  </si>
+  <si>
+    <t>INE217B01036</t>
+  </si>
+  <si>
     <t>Gillette India Ltd.</t>
   </si>
   <si>
     <t>INE322A01010</t>
   </si>
   <si>
-    <t>Eureka Forbes Ltd.</t>
-  </si>
-  <si>
-    <t>INE0KCE01017</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
+    <t>Sobha Ltd.</t>
+  </si>
+  <si>
+    <t>INE671H01015</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Relaxo Footwears Ltd.</t>
+  </si>
+  <si>
+    <t>INE131B01039</t>
+  </si>
+  <si>
+    <t>Bajaj Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE193E01025</t>
+  </si>
+  <si>
+    <t>Orient Electric Ltd.</t>
+  </si>
+  <si>
+    <t>INE142Z01019</t>
+  </si>
+  <si>
+    <t>Sai Silks (Kalamandir) Ltd.</t>
+  </si>
+  <si>
+    <t>INE438K01021</t>
+  </si>
+  <si>
+    <t>V-Guard Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE951I01027</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Sapphire Foods India Ltd</t>
+  </si>
+  <si>
+    <t>INE806T01020</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Somany Ceramics Ltd.</t>
+  </si>
+  <si>
+    <t>INE355A01028</t>
+  </si>
+  <si>
+    <t>Rolex Rings Ltd.</t>
+  </si>
+  <si>
+    <t>INE645S01016</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
   </si>
   <si>
     <t>Affle India Ltd.</t>
@@ -301,154 +463,16 @@
     <t>It - Services</t>
   </si>
   <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Honasa Consumer Ltd.</t>
-  </si>
-  <si>
-    <t>INE0J5401028</t>
-  </si>
-  <si>
-    <t>La Opala RG Ltd.</t>
-  </si>
-  <si>
-    <t>INE059D01020</t>
-  </si>
-  <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Sanofi Consumer Healthcare India Ltd</t>
-  </si>
-  <si>
-    <t>INE0UOS01011</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Relaxo Footwears Ltd.</t>
-  </si>
-  <si>
-    <t>INE131B01039</t>
-  </si>
-  <si>
-    <t>Whirlpool of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE716A01013</t>
-  </si>
-  <si>
-    <t>Procter &amp; Gamble Health Ltd.</t>
-  </si>
-  <si>
-    <t>INE199A01012</t>
-  </si>
-  <si>
-    <t>Sai Silks (Kalamandir) Ltd.</t>
-  </si>
-  <si>
-    <t>INE438K01021</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Sun TV Network Ltd.</t>
-  </si>
-  <si>
-    <t>INE424H01027</t>
-  </si>
-  <si>
-    <t>Kajaria Ceramics Ltd.</t>
-  </si>
-  <si>
-    <t>INE217B01036</t>
-  </si>
-  <si>
-    <t>Bajaj Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE193E01025</t>
-  </si>
-  <si>
-    <t>EIH Ltd.</t>
-  </si>
-  <si>
-    <t>INE230A01023</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Rolex Rings Ltd.</t>
-  </si>
-  <si>
-    <t>INE645S01016</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Orient Electric Ltd.</t>
-  </si>
-  <si>
-    <t>INE142Z01019</t>
-  </si>
-  <si>
-    <t>The Ethos Ltd.</t>
-  </si>
-  <si>
-    <t>INE04TZ01018</t>
-  </si>
-  <si>
-    <t>Medplus Health Services Ltd</t>
-  </si>
-  <si>
-    <t>INE804L01022</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>Somany Ceramics Ltd.</t>
-  </si>
-  <si>
-    <t>INE355A01028</t>
-  </si>
-  <si>
-    <t>Sapphire Foods India Ltd</t>
-  </si>
-  <si>
-    <t>INE806T01020</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd. (Covered call) $$</t>
+    <t>Schloss Bangalore Ltd.</t>
+  </si>
+  <si>
+    <t>INE0AQ201015</t>
+  </si>
+  <si>
+    <t>Metro Brands Ltd.</t>
+  </si>
+  <si>
+    <t>INE317I01021</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -484,13 +508,28 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>91 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z164</t>
+  </si>
+  <si>
     <t>182 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>SOV</t>
+    <t>IN002024Y407</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -523,16 +562,13 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>$$ - Derivatives.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -915,13 +951,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -939,7 +975,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21793200"/>
+          <a:off x="666750" y="22745700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -954,13 +990,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -978,7 +1014,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24650700"/>
+          <a:off x="666750" y="25603200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1312,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J126"/>
+  <dimension ref="B1:J131"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1412,10 +1448,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>287757.35000000003</v>
+        <v>291506.24999999994</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9237827958828001</v>
+        <v>0.9207208462328001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1449,10 +1485,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>287757.35000000003</v>
+        <v>291506.24999999994</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9237827958828001</v>
+        <v>0.9207208462328001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1475,13 +1511,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>1526797</v>
+        <v>1267488</v>
       </c>
       <c r="G8" s="15">
-        <v>24830.30</v>
+        <v>29764.42</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0797123130188</v>
+        <v>0.0940107526686</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1504,13 +1540,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>975488</v>
+        <v>728063</v>
       </c>
       <c r="G9" s="15">
-        <v>24082.85</v>
+        <v>21672.98</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0773127862967</v>
+        <v>0.0684539850725</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1533,13 +1569,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>154258</v>
+        <v>1115932</v>
       </c>
       <c r="G10" s="15">
-        <v>18990.16</v>
+        <v>20713.93</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0609638054392</v>
+        <v>0.0654248310575</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1559,16 +1595,16 @@
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>553063</v>
+        <v>4390146</v>
       </c>
       <c r="G11" s="15">
-        <v>16535.75</v>
+        <v>18353.01</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0530844524633</v>
+        <v>0.0579678785555</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1588,16 +1624,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F12" s="14">
-        <v>626613</v>
+        <v>121804</v>
       </c>
       <c r="G12" s="15">
-        <v>14494.81</v>
+        <v>15005.03</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0465324555832</v>
+        <v>0.0473933026115</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1608,25 +1644,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F13" s="14">
-        <v>3121829</v>
+        <v>5340091</v>
       </c>
       <c r="G13" s="15">
-        <v>13970.18</v>
+        <v>12725.97</v>
       </c>
       <c r="H13" s="16">
-        <v>0.044848244326</v>
+        <v>0.0401949044576</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1649,13 +1685,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>4820091</v>
+        <v>518359</v>
       </c>
       <c r="G14" s="15">
-        <v>10621.07</v>
+        <v>12420.92</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0340966503197</v>
+        <v>0.0392314057534</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1675,16 +1711,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F15" s="14">
-        <v>411543</v>
+        <v>322024</v>
       </c>
       <c r="G15" s="15">
-        <v>10115.32</v>
+        <v>10005.93</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0324730492231</v>
+        <v>0.0316036734614</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1695,25 +1731,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>185129</v>
+        <v>332035</v>
       </c>
       <c r="G16" s="15">
-        <v>9496.47</v>
+        <v>9233.23</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0304863650142</v>
+        <v>0.0291631048702</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1724,25 +1760,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F17" s="14">
-        <v>522607</v>
+        <v>150371</v>
       </c>
       <c r="G17" s="15">
-        <v>9114</v>
+        <v>8286.19</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0292585277203</v>
+        <v>0.0261718843725</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1762,16 +1798,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F18" s="14">
-        <v>307024</v>
+        <v>131205</v>
       </c>
       <c r="G18" s="15">
-        <v>8816.81</v>
+        <v>7404.55</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0283044634397</v>
+        <v>0.0233872294058</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1782,25 +1818,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="F19" s="14">
-        <v>349501</v>
+        <v>351742</v>
       </c>
       <c r="G19" s="15">
-        <v>7500.29</v>
+        <v>6953.24</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0240780604427</v>
+        <v>0.0219617693167</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1811,25 +1847,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F20" s="14">
-        <v>404659</v>
+        <v>842854</v>
       </c>
       <c r="G20" s="15">
-        <v>6337.77</v>
+        <v>6720.07</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0203460411707</v>
+        <v>0.021225303187</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1840,25 +1876,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F21" s="14">
-        <v>146057</v>
+        <v>385666</v>
       </c>
       <c r="G21" s="15">
-        <v>6337.63</v>
+        <v>6469.93</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0203455917309</v>
+        <v>0.020435237408</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1869,25 +1905,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F22" s="14">
-        <v>120186</v>
+        <v>1725000</v>
       </c>
       <c r="G22" s="15">
-        <v>6242.82</v>
+        <v>5759.78</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0200412247117</v>
+        <v>0.018192232639</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1907,16 +1943,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>3390894</v>
+        <v>790000</v>
       </c>
       <c r="G23" s="15">
-        <v>5727.22</v>
+        <v>5684.05</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0183860023184</v>
+        <v>0.0179530398612</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1936,16 +1972,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F24" s="14">
-        <v>790000</v>
+        <v>362254</v>
       </c>
       <c r="G24" s="15">
-        <v>5657.19</v>
+        <v>5531.62</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0181611861349</v>
+        <v>0.017471590566</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1956,25 +1992,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" s="14">
-        <v>1060969</v>
+        <v>1180346</v>
       </c>
       <c r="G25" s="15">
-        <v>5621.54</v>
+        <v>4590.37</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0180467395129</v>
+        <v>0.0144986577506</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1985,25 +2021,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="14">
-        <v>1094815</v>
+        <v>320109</v>
       </c>
       <c r="G26" s="15">
-        <v>5546.33</v>
+        <v>4563.79</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0178052940586</v>
+        <v>0.0144147049706</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2014,25 +2050,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F27" s="14">
-        <v>81205</v>
+        <v>668373</v>
       </c>
       <c r="G27" s="15">
-        <v>4671.89</v>
+        <v>4291.29</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0149980933806</v>
+        <v>0.0135540152577</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2043,25 +2079,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F28" s="14">
-        <v>402111</v>
+        <v>1145677</v>
       </c>
       <c r="G28" s="15">
-        <v>4508.67</v>
+        <v>3625.49</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0144741108379</v>
+        <v>0.0114510897135</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2072,25 +2108,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F29" s="14">
-        <v>9383</v>
+        <v>201785</v>
       </c>
       <c r="G29" s="15">
-        <v>4196.41</v>
+        <v>3523.77</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0134716675785</v>
+        <v>0.0111298076673</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2101,25 +2137,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F30" s="14">
-        <v>449008</v>
+        <v>982783</v>
       </c>
       <c r="G30" s="15">
-        <v>4192.84</v>
+        <v>3468.24</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0134602068649</v>
+        <v>0.0109544164756</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2130,25 +2166,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F31" s="14">
-        <v>320109</v>
+        <v>64304</v>
       </c>
       <c r="G31" s="15">
-        <v>3924.54</v>
+        <v>3429.65</v>
       </c>
       <c r="H31" s="16">
-        <v>0.012598887687</v>
+        <v>0.0108325301783</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2159,25 +2195,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F32" s="14">
-        <v>504726</v>
+        <v>1612757</v>
       </c>
       <c r="G32" s="15">
-        <v>3406.14</v>
+        <v>3278.09</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0109346764987</v>
+        <v>0.0103538287732</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2188,25 +2224,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F33" s="14">
-        <v>307415</v>
+        <v>660969</v>
       </c>
       <c r="G33" s="15">
-        <v>3352.36</v>
+        <v>3192.15</v>
       </c>
       <c r="H33" s="16">
-        <v>0.010762027429</v>
+        <v>0.010082387768</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2226,16 +2262,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="F34" s="14">
-        <v>139246</v>
+        <v>1160000</v>
       </c>
       <c r="G34" s="15">
-        <v>3203.77</v>
+        <v>3190</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0102850113401</v>
+        <v>0.0100755970051</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2246,25 +2282,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="F35" s="14">
-        <v>36237</v>
+        <v>6769</v>
       </c>
       <c r="G35" s="15">
-        <v>3119.01</v>
+        <v>3139.46</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0100129076744</v>
+        <v>0.0099159667002</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2275,25 +2311,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="F36" s="14">
-        <v>584281</v>
+        <v>70557</v>
       </c>
       <c r="G36" s="15">
-        <v>3109.84</v>
+        <v>3040.51</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0099834693708</v>
+        <v>0.0096034336834</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2304,25 +2340,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F37" s="14">
-        <v>1160000</v>
+        <v>307415</v>
       </c>
       <c r="G37" s="15">
-        <v>3093.14</v>
+        <v>3028.81</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0099298576292</v>
+        <v>0.0095664792994</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2333,25 +2369,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F38" s="14">
-        <v>317824</v>
+        <v>245122</v>
       </c>
       <c r="G38" s="15">
-        <v>3083.69</v>
+        <v>3018.43</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0098995204461</v>
+        <v>0.009533694128</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2362,25 +2398,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="F39" s="14">
-        <v>184816</v>
+        <v>317824</v>
       </c>
       <c r="G39" s="15">
-        <v>2786.93</v>
+        <v>2955.76</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0089468365876</v>
+        <v>0.0093357512865</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2391,25 +2427,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="F40" s="14">
-        <v>150000</v>
+        <v>2078904</v>
       </c>
       <c r="G40" s="15">
-        <v>2718.98</v>
+        <v>2788.85</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0087286977947</v>
+        <v>0.008808566993</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2429,16 +2465,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F41" s="14">
-        <v>1145677</v>
+        <v>698034</v>
       </c>
       <c r="G41" s="15">
-        <v>2521.64</v>
+        <v>2741.88</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0080951803643</v>
+        <v>0.008660212513</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2458,16 +2494,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F42" s="14">
         <v>815236</v>
       </c>
       <c r="G42" s="15">
-        <v>2209.7</v>
+        <v>2005.07</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0070937643958</v>
+        <v>0.0063330022843</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2487,16 +2523,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F43" s="14">
         <v>37821</v>
       </c>
       <c r="G43" s="15">
-        <v>1914.90</v>
+        <v>1928.30</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0061473726938</v>
+        <v>0.0060905246724</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2516,16 +2552,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F44" s="14">
-        <v>38948</v>
+        <v>34948</v>
       </c>
       <c r="G44" s="15">
-        <v>1825.82</v>
+        <v>1841.27</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0058614006015</v>
+        <v>0.0058156409083</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2545,16 +2581,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F45" s="14">
-        <v>148607</v>
+        <v>141719</v>
       </c>
       <c r="G45" s="15">
-        <v>1809.07</v>
+        <v>1751.51</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0058076283457</v>
+        <v>0.0055321344547</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2574,16 +2610,16 @@
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F46" s="14">
-        <v>307585</v>
+        <v>74246</v>
       </c>
       <c r="G46" s="15">
-        <v>1690.03</v>
+        <v>1677.29</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0054254761469</v>
+        <v>0.0052977110033</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2603,16 +2639,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F47" s="14">
-        <v>141719</v>
+        <v>27552</v>
       </c>
       <c r="G47" s="15">
-        <v>1615.31</v>
+        <v>1583.69</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0051856037318</v>
+        <v>0.0050020759313</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2632,16 +2668,16 @@
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F48" s="14">
-        <v>29191</v>
+        <v>152086</v>
       </c>
       <c r="G48" s="15">
-        <v>1571.23</v>
+        <v>1581.31</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0050440944162</v>
+        <v>0.0049945587148</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2661,16 +2697,16 @@
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="F49" s="14">
-        <v>917462</v>
+        <v>16541</v>
       </c>
       <c r="G49" s="15">
-        <v>1552.53</v>
+        <v>1558.66</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0049840621068</v>
+        <v>0.0049230188175</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2690,16 +2726,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F50" s="14">
-        <v>128225</v>
+        <v>105049</v>
       </c>
       <c r="G50" s="15">
-        <v>1502.67</v>
+        <v>1505.35</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0048239973501</v>
+        <v>0.0047546394833</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2719,16 +2755,16 @@
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F51" s="14">
-        <v>241449</v>
+        <v>76500</v>
       </c>
       <c r="G51" s="15">
-        <v>1494.21</v>
+        <v>1497.64</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0047968383481</v>
+        <v>0.0047302874918</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2748,16 +2784,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F52" s="14">
-        <v>142303</v>
+        <v>103000</v>
       </c>
       <c r="G52" s="15">
-        <v>1410.79</v>
+        <v>1470.33</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0045290364628</v>
+        <v>0.0046440290108</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2777,16 +2813,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F53" s="14">
-        <v>182147</v>
+        <v>111107</v>
       </c>
       <c r="G53" s="15">
-        <v>1276.12</v>
+        <v>1390.17</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0040967075262</v>
+        <v>0.004390844103</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2806,16 +2842,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="F54" s="14">
-        <v>271399</v>
+        <v>307585</v>
       </c>
       <c r="G54" s="15">
-        <v>1005.53</v>
+        <v>1344.30</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0032280367981</v>
+        <v>0.0042459639667</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2826,25 +2862,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="F55" s="14">
-        <v>49636</v>
+        <v>182147</v>
       </c>
       <c r="G55" s="15">
-        <v>892.60</v>
+        <v>1250.80</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0028654994341</v>
+        <v>0.0039506447442</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2855,25 +2891,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F56" s="14">
-        <v>381530</v>
+        <v>522312</v>
       </c>
       <c r="G56" s="15">
-        <v>838.03</v>
+        <v>1185.07</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0026903142402</v>
+        <v>0.00374303691</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2884,25 +2920,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F57" s="14">
-        <v>33134</v>
+        <v>879001</v>
       </c>
       <c r="G57" s="15">
-        <v>805.60</v>
+        <v>1117.56</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0025862047324</v>
+        <v>0.0035298069558</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -2913,25 +2949,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F58" s="14">
-        <v>108988</v>
+        <v>291468</v>
       </c>
       <c r="G58" s="15">
-        <v>788.36</v>
+        <v>1105.68</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0025308594375</v>
+        <v>0.0034922840428</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -2942,25 +2978,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F59" s="14">
-        <v>45049</v>
+        <v>90225</v>
       </c>
       <c r="G59" s="15">
-        <v>666.45</v>
+        <v>1035.6</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0021394937238</v>
+        <v>0.0032709367581</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -2971,25 +3007,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="F60" s="14">
-        <v>85959</v>
+        <v>286930</v>
       </c>
       <c r="G60" s="15">
-        <v>438.39</v>
+        <v>912.72</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0014073563712</v>
+        <v>0.0028828209713</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3000,25 +3036,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>141</v>
-      </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="F61" s="14">
-        <v>122720</v>
+        <v>189339</v>
       </c>
       <c r="G61" s="15">
-        <v>355.40</v>
+        <v>905.61</v>
       </c>
       <c r="H61" s="16">
-        <v>0.001140934908</v>
+        <v>0.0028603640764</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3029,25 +3065,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="D62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="F62" s="14">
-        <v>171609</v>
+        <v>49636</v>
       </c>
       <c r="G62" s="15">
-        <v>279.64</v>
+        <v>795.62</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0008977237976</v>
+        <v>0.0025129612819</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3060,21 +3096,23 @@
       <c r="B63" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="13"/>
+      <c r="C63" s="13" t="s">
+        <v>145</v>
+      </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F63" s="14">
-        <v>-52000</v>
+        <v>33999</v>
       </c>
       <c r="G63" s="15">
-        <v>-113.39</v>
+        <v>498.32</v>
       </c>
       <c r="H63" s="16">
-        <v>-0.0003640140946</v>
+        <v>0.0015739409089</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3085,6 +3123,27 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="14">
+        <v>24535</v>
+      </c>
+      <c r="G64" s="15">
+        <v>425.83</v>
+      </c>
+      <c r="H64" s="16">
+        <v>0.0013449816528</v>
+      </c>
+      <c r="I64" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="11" t="s">
@@ -3092,28 +3151,28 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I65" s="9" t="s">
+      <c r="B65" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" s="14">
+        <v>66525</v>
+      </c>
+      <c r="G65" s="15">
+        <v>289.38</v>
+      </c>
+      <c r="H65" s="16">
+        <v>0.0009140050976</v>
+      </c>
+      <c r="I65" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
@@ -3122,6 +3181,27 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F66" s="14">
+        <v>23020</v>
+      </c>
+      <c r="G66" s="15">
+        <v>277.78</v>
+      </c>
+      <c r="H66" s="16">
+        <v>0.000877366563</v>
+      </c>
+      <c r="I66" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="11" t="s">
@@ -3129,28 +3209,7 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I67" s="9" t="s">
+      <c r="B67" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J67" s="11" t="s">
@@ -3158,7 +3217,28 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I68" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J68" s="11" t="s">
@@ -3166,73 +3246,73 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1">
+      <c r="B70" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1">
+      <c r="B71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" ht="15" customHeight="1">
-      <c r="B70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I72" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -3240,28 +3320,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I73" s="9" t="s">
+      <c r="B73" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J73" s="11" t="s">
@@ -3269,7 +3328,28 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I74" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J74" s="11" t="s">
@@ -3277,28 +3357,7 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I75" s="9" t="s">
+      <c r="B75" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J75" s="11" t="s">
@@ -3306,7 +3365,28 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I76" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J76" s="11" t="s">
@@ -3314,28 +3394,7 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I77" s="9" t="s">
+      <c r="B77" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="11" t="s">
@@ -3343,7 +3402,28 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I78" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J78" s="11" t="s">
@@ -3351,28 +3431,7 @@
       </c>
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="9">
-        <v>3197.21</v>
-      </c>
-      <c r="H79" s="10">
-        <v>0.0102639518776</v>
-      </c>
-      <c r="I79" s="9" t="s">
+      <c r="B79" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J79" s="11" t="s">
@@ -3380,7 +3439,28 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="11" t="s">
@@ -3388,28 +3468,7 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I81" s="9" t="s">
+      <c r="B81" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3417,7 +3476,28 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9">
+        <v>4667.81</v>
+      </c>
+      <c r="H82" s="10">
+        <v>0.0147432515537</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3425,36 +3505,36 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
+      <c r="H84" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J84" s="11" t="s">
@@ -3462,28 +3542,7 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9">
-        <v>3197.21</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0.0102639518776</v>
-      </c>
-      <c r="I85" s="9" t="s">
+      <c r="B85" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J85" s="11" t="s">
@@ -3491,29 +3550,29 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F86" s="14">
-        <v>3200000</v>
-      </c>
-      <c r="G86" s="15">
-        <v>3197.21</v>
-      </c>
-      <c r="H86" s="16">
-        <v>0.0102639518776</v>
-      </c>
-      <c r="I86" s="15">
-        <v>6.37</v>
+      <c r="B86" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -3529,7 +3588,7 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>13</v>
@@ -3544,10 +3603,10 @@
         <v>13</v>
       </c>
       <c r="G88" s="9">
-        <v>6591.03</v>
+        <v>4667.81</v>
       </c>
       <c r="H88" s="10">
-        <v>0.0211590776783</v>
+        <v>0.0147432515537</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>13</v>
@@ -3558,28 +3617,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F89" s="14">
-        <v>1780686</v>
+        <v>2550000</v>
       </c>
       <c r="G89" s="15">
-        <v>6591.03</v>
+        <v>2532.09</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0211590776783</v>
-      </c>
-      <c r="I89" s="15" t="s">
-        <v>13</v>
+        <v>0.0079975919814</v>
+      </c>
+      <c r="I89" s="15">
+        <v>5.61</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -3587,36 +3646,57 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>13</v>
+        <v>164</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F90" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="G90" s="15">
+        <v>993.90</v>
+      </c>
+      <c r="H90" s="16">
+        <v>0.0031392275434</v>
+      </c>
+      <c r="I90" s="15">
+        <v>5.60</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
+      <c r="B91" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F91" s="14">
+        <v>700000</v>
+      </c>
+      <c r="G91" s="15">
+        <v>694.98</v>
+      </c>
+      <c r="H91" s="16">
+        <v>0.0021950904096</v>
+      </c>
+      <c r="I91" s="15">
+        <v>5.61</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -3624,35 +3704,35 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>13</v>
+        <v>170</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F92" s="14">
+        <v>450000</v>
+      </c>
+      <c r="G92" s="15">
+        <v>446.84</v>
+      </c>
+      <c r="H92" s="16">
+        <v>0.0014113416193</v>
+      </c>
+      <c r="I92" s="15">
+        <v>5.61</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9">
-        <v>10675.04</v>
-      </c>
-      <c r="H93" s="10">
-        <v>0.0342699093433</v>
-      </c>
-      <c r="I93" s="9" t="s">
+      <c r="B93" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J93" s="11" t="s">
@@ -3660,7 +3740,28 @@
       </c>
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="9">
+        <v>5265.94</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0.0166324417847</v>
+      </c>
+      <c r="I94" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
@@ -3668,28 +3769,28 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9">
-        <v>442.5136746999999</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0.0014205945378</v>
-      </c>
-      <c r="I95" s="9" t="s">
+      <c r="B95" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F95" s="14">
+        <v>1380686</v>
+      </c>
+      <c r="G95" s="15">
+        <v>5265.94</v>
+      </c>
+      <c r="H95" s="16">
+        <v>0.0166324417847</v>
+      </c>
+      <c r="I95" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
@@ -3698,20 +3799,6 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13"/>
-      <c r="G96" s="15">
-        <v>442.5136746999999</v>
-      </c>
-      <c r="H96" s="16">
-        <v>0.0014205945378</v>
-      </c>
-      <c r="I96" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
@@ -3719,7 +3806,28 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I97" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
@@ -3727,156 +3835,248 @@
       </c>
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="18">
-        <v>2835.78365089983</v>
-      </c>
-      <c r="H98" s="19">
-        <v>0.009103670677927165</v>
-      </c>
-      <c r="I98" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J98" s="20" t="s">
+      <c r="B98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="18">
-        <v>311498.9273256</v>
-      </c>
-      <c r="H99" s="19">
-        <v>0.9999999999977273</v>
-      </c>
-      <c r="I99" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J99" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" ht="15" customHeight="1">
-      <c r="B102" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-      <c r="I102" s="21"/>
-    </row>
-    <row r="103" spans="2:8" ht="15" customHeight="1">
-      <c r="B103" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-    </row>
-    <row r="104" spans="2:8" ht="15" customHeight="1">
-      <c r="B104" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-    </row>
-    <row r="105" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B105" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="21"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
-    </row>
-    <row r="106" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B106" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="21"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="21"/>
-    </row>
-    <row r="107" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B107" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-    </row>
-    <row r="110" ht="15">
-      <c r="B110" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="125" ht="15">
-      <c r="B125" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="126" ht="15">
-      <c r="B126" s="21" t="s">
+      <c r="B99" s="7" t="s">
         <v>176</v>
       </c>
+      <c r="C99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="9">
+        <v>15692.51</v>
+      </c>
+      <c r="H99" s="10">
+        <v>0.0495647043134</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15" customHeight="1">
+      <c r="B100" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15" customHeight="1">
+      <c r="B101" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
+        <v>1142.5136747</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.0036086229966</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15" customHeight="1">
+      <c r="B102" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C102" s="13"/>
+      <c r="D102" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="13"/>
+      <c r="G102" s="15">
+        <v>1142.5136747</v>
+      </c>
+      <c r="H102" s="16">
+        <v>0.0036086229966</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15" customHeight="1">
+      <c r="B103" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15" customHeight="1">
+      <c r="B104" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="18">
+        <v>-1668.4743695898214</v>
+      </c>
+      <c r="H104" s="19">
+        <v>-0.005269866884471591</v>
+      </c>
+      <c r="I104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" ht="15" customHeight="1">
+      <c r="B105" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="18">
+        <v>316606.54930511</v>
+      </c>
+      <c r="H105" s="19">
+        <v>0.9999999999967283</v>
+      </c>
+      <c r="I105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" ht="15" customHeight="1">
+      <c r="B108" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="21"/>
+      <c r="G108" s="21"/>
+      <c r="H108" s="21"/>
+      <c r="I108" s="21"/>
+    </row>
+    <row r="109" spans="2:8" ht="15" customHeight="1">
+      <c r="B109" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="21"/>
+      <c r="G109" s="21"/>
+      <c r="H109" s="21"/>
+    </row>
+    <row r="110" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B110" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="21"/>
+      <c r="G110" s="21"/>
+      <c r="H110" s="21"/>
+    </row>
+    <row r="111" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B111" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C111" s="21"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="21"/>
+      <c r="G111" s="21"/>
+      <c r="H111" s="21"/>
+    </row>
+    <row r="112" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B112" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C112" s="21"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="21"/>
+      <c r="F112" s="21"/>
+      <c r="G112" s="21"/>
+      <c r="H112" s="21"/>
+    </row>
+    <row r="115" ht="15">
+      <c r="B115" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="130" ht="15">
+      <c r="B130" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="131" ht="15">
+      <c r="B131" s="21" t="s">
+        <v>188</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B104:H104"/>
-    <mergeCell ref="B105:H105"/>
-    <mergeCell ref="B106:H106"/>
-    <mergeCell ref="B107:H107"/>
+  <mergeCells count="8">
+    <mergeCell ref="B110:H110"/>
+    <mergeCell ref="B111:H111"/>
+    <mergeCell ref="B112:H112"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B102:I102"/>
-    <mergeCell ref="B103:H103"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="B109:H109"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
